--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -454,23 +454,25 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>17.30087</v>
+        <v>17.71998</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24225</v>
+        <v>17.15526</v>
       </c>
       <c r="E2" t="n">
-        <v>17.55799</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.89403</v>
+        <v>17.19976</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05395</v>
+        <v>0.05262</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91225</v>
+        <v>1.89424</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.48296</v>
+        <v>17.40096</v>
       </c>
       <c r="D3" t="n">
-        <v>17.40812</v>
+        <v>16.98324</v>
       </c>
       <c r="E3" t="n">
-        <v>17.4251</v>
+        <v>17.34331</v>
       </c>
       <c r="F3" t="n">
-        <v>44.33655</v>
+        <v>43.90197</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05344</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90173</v>
+        <v>1.90958</v>
       </c>
     </row>
     <row r="4">
@@ -504,23 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>17.5854</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>17.19502</v>
+        <v>17.2695</v>
       </c>
       <c r="E4" t="n">
-        <v>17.30129</v>
+        <v>17.66856</v>
       </c>
       <c r="F4" t="n">
-        <v>44.31598</v>
+        <v>45.16576</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05381</v>
+        <v>0.05335</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86671</v>
+        <v>1.92733</v>
       </c>
     </row>
     <row r="5">
@@ -529,23 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>17.60291</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>17.45464</v>
+        <v>17.30671</v>
       </c>
       <c r="E5" t="n">
-        <v>17.45259</v>
+        <v>17.41391</v>
       </c>
       <c r="F5" t="n">
-        <v>42.94903</v>
+        <v>44.09811</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05277</v>
+        <v>0.05321</v>
       </c>
       <c r="H5" t="n">
-        <v>1.88945</v>
+        <v>1.92162</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.2786</v>
+        <v>17.83182</v>
       </c>
       <c r="D6" t="n">
-        <v>17.14049</v>
+        <v>17.37863</v>
       </c>
       <c r="E6" t="n">
-        <v>17.71411</v>
+        <v>17.73053</v>
       </c>
       <c r="F6" t="n">
-        <v>43.877</v>
+        <v>44.59394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05294</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.92962</v>
+        <v>0.05397</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.53808</v>
+        <v>17.47927</v>
       </c>
       <c r="D7" t="n">
-        <v>17.24868</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.33276</v>
+        <v>17.26614</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>44.41594</v>
+        <v>44.82268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0533</v>
+        <v>0.05275</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94388</v>
+        <v>1.90249</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.88098</v>
+        <v>17.61977</v>
       </c>
       <c r="D8" t="n">
-        <v>17.29851</v>
+        <v>17.15696</v>
       </c>
       <c r="E8" t="n">
-        <v>17.35212</v>
+        <v>17.44924</v>
       </c>
       <c r="F8" t="n">
-        <v>44.21382</v>
+        <v>44.74161</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05178</v>
+        <v>0.05282</v>
       </c>
       <c r="H8" t="n">
-        <v>1.93227</v>
+        <v>1.92833</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.18161</v>
+        <v>17.6861</v>
       </c>
       <c r="D9" t="n">
-        <v>17.48943</v>
+        <v>17.25081</v>
       </c>
       <c r="E9" t="n">
-        <v>17.57782</v>
+        <v>17.62274</v>
       </c>
       <c r="F9" t="n">
-        <v>44.63264</v>
+        <v>44.61951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05311</v>
+        <v>0.05456</v>
       </c>
       <c r="H9" t="n">
-        <v>1.88243</v>
+        <v>1.92266</v>
       </c>
     </row>
     <row r="10">
@@ -655,51 +663,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.59355</v>
+        <v>17.65299</v>
       </c>
       <c r="D10" t="n">
-        <v>17.20118</v>
+        <v>17.36203</v>
       </c>
       <c r="E10" t="n">
-        <v>17.53244</v>
+        <v>17.53256</v>
       </c>
       <c r="F10" t="n">
-        <v>43.33527</v>
+        <v>44.67621</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05239</v>
+        <v>0.05244</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89411</v>
+        <v>1.91591</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -713,26 +701,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.05213</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>17.32718</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.55505</v>
-      </c>
-      <c r="F12" t="n">
-        <v>44.27477</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05367</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.92529</v>
+        <v>1.15059</v>
       </c>
     </row>
     <row r="13">
@@ -742,22 +718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.59625</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>17.42307</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.47725</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44.77116</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0529</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.94776</v>
+        <v>1.14394</v>
       </c>
     </row>
     <row r="14">
@@ -767,22 +731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.43703</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>16.91346</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.67162</v>
-      </c>
-      <c r="F14" t="n">
-        <v>45.0738</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05336</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.92932</v>
+        <v>1.14414</v>
       </c>
     </row>
     <row r="15">
@@ -792,22 +744,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.84017</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17.27106</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.49679</v>
-      </c>
-      <c r="F15" t="n">
-        <v>45.62873</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05339</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.93555</v>
+        <v>1.16242</v>
       </c>
     </row>
     <row r="16">
@@ -817,22 +757,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.60464</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>17.63777</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.24568</v>
-      </c>
-      <c r="F16" t="n">
-        <v>44.27435</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05301</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.87968</v>
+        <v>1.16794</v>
       </c>
     </row>
     <row r="17">
@@ -842,22 +770,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.59057</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>17.34618</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.66239</v>
-      </c>
-      <c r="F17" t="n">
-        <v>44.01101</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05179</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.92467</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="18">
@@ -867,22 +783,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.75905</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>17.77938</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.14267</v>
-      </c>
-      <c r="F18" t="n">
-        <v>44.98562</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05264</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.88146</v>
+        <v>1.15707</v>
       </c>
     </row>
     <row r="19">
@@ -892,22 +796,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.41843</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>17.57513</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.65557</v>
-      </c>
-      <c r="F19" t="n">
-        <v>44.61035</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05294</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.91196</v>
+        <v>1.18683</v>
       </c>
     </row>
     <row r="20">
@@ -917,22 +809,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.57256</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17.35424</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17.95295</v>
-      </c>
-      <c r="F20" t="n">
-        <v>45.37297</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05323</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.88135</v>
+        <v>1.17462</v>
       </c>
     </row>
   </sheetData>
